--- a/evaluation-analysis.xlsx
+++ b/evaluation-analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>ODRL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Output</t>
         </is>
       </c>
     </row>
@@ -539,6 +544,25 @@
 }</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P01-1",
+  "evaluationRequest": "ex:request/P01-1",
+  "policy": "ex:57d3ec9f-3f32-433c-86b2-4b81fcb09540",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "doctor2 belongs to the medical-staff PartyCollection (sch:Physician). The permission is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -636,6 +660,25 @@
 }</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P01-2",
+  "evaluationRequest": "ex:request/P01-2",
+  "policy": "ex:57d3ec9f-3f32-433c-86b2-4b81fcb09540",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "administrative1 does not belong to the medical-staff PartyCollection (sch:Physician). The permission is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -736,6 +779,25 @@
 }</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P02-4",
+  "evaluationRequest": "ex:request/P02-4",
+  "policy": "ex:policy/P02",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "nurse1 does not belong to the admin-staff PartyCollection (coral:SystemAdministrator). The permission for odrl:delete on db:EmployeeRecords is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -836,6 +898,25 @@
 }</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P02-2",
+  "evaluationRequest": "ex:request/P02-2",
+  "policy": "ex:policy/P02",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "nurse1 does not belong to the admin-staff PartyCollection (coral:SystemAdministrator). The permission for odrl:modify on db:EmployeeRecords is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -936,6 +1017,25 @@
 }</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P02-3",
+  "evaluationRequest": "ex:request/P02-3",
+  "policy": "ex:policy/P02",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "administrator1 belongs to the admin-staff PartyCollection (coral:SystemAdministrator). The permission for odrl:delete on db:EmployeeRecords is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1036,6 +1136,25 @@
 }</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P02-1",
+  "evaluationRequest": "ex:request/P02-1",
+  "policy": "ex:policy/P02",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "administrator1 belongs to the admin-staff PartyCollection (coral:SystemAdministrator). The permission for odrl:modify on db:EmployeeRecords is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1166,6 +1285,25 @@
 </t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P03-4",
+  "evaluationRequest": "ex:request/P03-4",
+  "policy": "ex:policy/P03",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "undefined",
+  "rdfs:comment": "doctor1 does not belong to the auditors PartyCollection (coral:Auditor). The prohibition does not apply to this party. No rule covers this case. Decision: undefined (neither permitted nor explicitly forbidden by this policy)."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1296,6 +1434,25 @@
 </t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P03-6",
+  "evaluationRequest": "ex:request/P03-6",
+  "policy": "ex:policy/P03",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "undefined",
+  "rdfs:comment": "doctor1 does not belong to the auditors PartyCollection (coral:Auditor). The prohibition does not apply to this party. No rule covers this case. Decision: undefined."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1426,6 +1583,25 @@
 </t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P03-2",
+  "evaluationRequest": "ex:request/P03-2",
+  "policy": "ex:policy/P03",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "doctor1 does not belong to the auditors PartyCollection (coral:Auditor). Neither the permission nor the prohibition applies to this party. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1556,6 +1732,25 @@
 </t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P03-5",
+  "evaluationRequest": "ex:request/P03-5",
+  "policy": "ex:policy/P03",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "forbid",
+  "rdfs:comment": "auditor1 belongs to the auditors PartyCollection (coral:Auditor). The prohibition for odrl:delete on db:BillingInformation is satisfied and active. Decision: forbid."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1686,6 +1881,25 @@
 </t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P03-3",
+  "evaluationRequest": "ex:request/P03-3",
+  "policy": "ex:policy/P03",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "forbid",
+  "rdfs:comment": "auditor1 belongs to the auditors PartyCollection (coral:Auditor). The prohibition for odrl:modify on db:BillingInformation is satisfied and active. Decision: forbid."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1812,6 +2026,25 @@
       ]
     }
   ]
+}
+</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P03-1",
+  "evaluationRequest": "ex:request/P03-1",
+  "policy": "ex:policy/P03",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "auditor1 belongs to the auditors PartyCollection (coral:Auditor). The permission for odrl:read on db:ClinicalRecords is satisfied and active. No prohibition is triggered. Decision: permit."
 }
 </t>
         </is>
@@ -1935,6 +2168,25 @@
 </t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P04-2",
+  "evaluationRequest": "ex:request/P04-2",
+  "policy": "ex:dc851af8-9798-4221-b79b-e0cbf6216d81",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "patient1 belongs to the patients PartyCollection (sch:Patient). However, the param-identity value (33512354C) does not match the patient_id of the requested clinical record (param-record: XXX-AB), which belongs to a different patient. The identity constraint is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2054,6 +2306,25 @@
 </t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P04-1",
+  "evaluationRequest": "ex:request/P04-1",
+  "policy": "ex:dc851af8-9798-4221-b79b-e0cbf6216d81",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "patient1 belongs to the patients PartyCollection (sch:Patient). The param-identity value (33512354C) matches the patient_id of the requested clinical record (param-record: 33X-AF). Both constraints are satisfied. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2178,6 +2449,25 @@
 </t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P05-2",
+  "evaluationRequest": "ex:request/P05-2",
+  "policy": "ex:policy/P05",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "doctor2 belongs to the medical-staff PartyCollection (sch:Physician). However, the param-physician-identity (ex:id/staff/physician/doctor2) does not match the assigned_doctor_id of the clinical record associated with patient 33512354C (which is doctor1). The identity constraint is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2298,6 +2588,25 @@
       ]
     }
   ]
+}
+</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P05-1",
+  "evaluationRequest": "ex:request/P05-1",
+  "policy": "ex:policy/P05",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "doctor1 belongs to the medical-staff PartyCollection (sch:Physician). The param-physician-identity (ex:id/staff/physician/doctor1) matches the assigned_doctor_id of the clinical record associated with patient 33512354C. The identity constraint is satisfied. Decision: permit."
 }
 </t>
         </is>
@@ -2423,6 +2732,25 @@
 </t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P06-1",
+  "evaluationRequest": "ex:request/P06-1",
+  "policy": "ex:policy/P06",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "head-cardiology1 belongs to the dept-heads PartyCollection (coral:DepartmentPhysicianHead). The param-department value (CARDIOLOGY) matches the department of the patient identified by 33512354C. The department constraint is satisfied. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2544,6 +2872,25 @@
 </t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P06-2",
+  "evaluationRequest": "ex:request/P06-2",
+  "policy": "ex:policy/P06",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "head-cardiology1 belongs to the dept-heads PartyCollection (coral:DepartmentPhysicianHead). However, the param-department value (ONCOLOGY) does not match the department of the patient identified by 33512354C (CARDIOLOGY). The department constraint is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2556,7 +2903,98 @@
           <t>ex:90782d9b-ebfa-4515-8473-ddb51ecbc3c1</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/ formal-semantics/ontology/evaluation_request.json",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationRequest",
+  "@id": "ex:request/P07-3",
+  "evaluatedAction": "odrl:read",
+  "evaluatedParty": "ex:id/staff/physician/doctor1",
+  "evaluatedTarget": "db:ClinicalRecords?patient_status='CRITIC'"
+}
+</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
+    {
+      "ex:patientStatus": {
+        "@type": "xsd:string"
+      }
+    }
+  ],
+  "@type": "odrl:Set",
+  "uid": "ex:90782d9b-ebfa-4515-8473-ddb51ecbc3c1",
+  "rdfs:label" : "Policy 07",
+  "permission": [
+    {
+      "@type": "odrl:Permission",
+      "assigner": {
+        "@type": [
+          "odrl:Party",
+          "sch:Hospital"
+        ],
+        "uid": "ex:hopital-organization",
+        "rdfs:description" : "A specific hospital that owns this policy"
+      },
+      "assignee": {
+        "@type": [
+          "odrl:PartyCollection",
+          "coral:EmergencyPhysician"
+        ],
+        "uid": "ex:groups/er-staff",
+        "rdfs:description" : "Anyone who belongs to the medical emergency physician team"
+      },
+      "action": "read",
+      "target": "db:ClinicalRecords?patient_status='CRITIC'|patient_status='EMERGENCY'"
+    }
+  ]
+}
+</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P07-3",
+  "evaluationRequest": "ex:request/P07-3",
+  "policy": "ex:90782d9b-ebfa-4515-8473-ddb51ecbc3c1",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "doctor1 does not belong to the er-staff PartyCollection (coral:EmergencyPhysician). The permission applies exclusively to emergency physicians. Even though the patient status is CRITIC, the assignee constraint is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P07_Emergency_Access_by_Emergency_Break-the-Glass</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ex:90782d9b-ebfa-4515-8473-ddb51ecbc3c1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -2583,7 +3021,7 @@
 </t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -2595,12 +3033,12 @@
   "@id": "ex:request/P07-1",
   "evaluatedAction": "odrl:read",
   "evaluatedParty": "ex:id/staff/physician/emergency_physician",
-  "evaluatedTarget": "db:PatientsRegistry",
-}
-</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+  "evaluatedTarget": "db:ClinicalRecords?patient_status='CRITIC'"
+}
+</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -2642,19 +3080,38 @@
 </t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P07-1",
+  "evaluationRequest": "ex:request/P07-1",
+  "policy": "ex:90782d9b-ebfa-4515-8473-ddb51ecbc3c1",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "emergency_physician belongs to the er-staff PartyCollection (coral:EmergencyPhysician). The target db:ClinicalRecords?patient_status='CRITIC' satisfies the filtered asset condition (status is CRITIC, which is included in CRITIC|EMERGENCY). The permission for odrl:read is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>P07_Emergency_Access_by_Emergency_Break-the-Glass</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>ex:90782d9b-ebfa-4515-8473-ddb51ecbc3c1</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -2681,7 +3138,7 @@
 </t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -2691,14 +3148,14 @@
   ],
   "@type": "EvaluationRequest",
   "@id": "ex:request/P07-2",
-  "evaluatedAction": "odrl:modify",
+  "evaluatedAction": "odrl:read",
   "evaluatedParty": "ex:id/staff/physician/emergency_physician",
-  "evaluatedTarget": "db:PatientsRegistry"
-}
-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+  "evaluatedTarget": "db:ClinicalRecords?patient_status='STABLE'"
+}
+</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -2740,19 +3197,38 @@
 </t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P07-2",
+  "evaluationRequest": "ex:request/P07-2",
+  "policy": "ex:90782d9b-ebfa-4515-8473-ddb51ecbc3c1",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "emergency_physician belongs to the er-staff PartyCollection (coral:EmergencyPhysician). However, the target db:ClinicalRecords?patient_status='STABLE' does not satisfy the filtered asset condition (STABLE is not in CRITIC|EMERGENCY). The target condition is not met. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>P08_Research_Anonymized_Data_Only</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>ex:5b5bf495-f6c4-4511-b94f-87410e55d947</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -2779,7 +3255,7 @@
 </t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -2788,25 +3264,20 @@
     "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "EvaluationRequest",
-  "@id": "ex:request/P08-1",
+  "@id": "ex:request/P08-2",
   "evaluatedAction": "odrl:read",
-  "evaluatedParty": "ex:id/staff/physician/doctor2",
-  "evaluatedTarget": "db:ClinicalRecords",
-}
-</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:isAnonymized": {
-        "@type": "xsd:boolean"
-      }
-    }
+  "evaluatedParty": "ex:id/staff/researcher/researcher1",
+  "evaluatedTarget": "db:ClinicalRecords?isAnonymized='False'"
+}
+</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "odrl:Set",
   "uid": "ex:5b5bf495-f6c4-4511-b94f-87410e55d947",
@@ -2831,26 +3302,157 @@
         "rdfs:description": "Any person who is part of the hospital research team"
       },
       "action": "read",
-      "target": "db:ClinicalRecords?isAnonymized='True'&amp;records"
+      "target": "db:ClinicalRecords?isAnonymized='True'"
     }
   ]
 }
 </t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P08-2",
+  "evaluationRequest": "ex:request/P08-2",
+  "policy": "ex:policy/P08",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "researcher1 belongs to the researchers PartyCollection (coral:HospitalResearchMember). However, the target db:ClinicalRecords?isAnonymized='False' does not satisfy the filtered asset condition (only anonymised records are permitted). Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>P08_Research_Anonymized_Data_Only</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>ex:5b5bf495-f6c4-4511-b94f-87410e55d947</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context" : [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/formal-semantics/ontology/stow.json",
+     "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
+    { "@context" : { "member" : { "@id" : "odrl:member", "@type" : "@id" } }}
+  ],
+  "@id" : "ex:StateP08-2",
+  "@type" : "SotW",
+  "context" :  {
+    "@id" : "ex:groups/researchers",
+    "@type" : "odrl:PartyCollection",
+    "rdfs:label" : "Hospital Resercher Team",
+    "member" : [ {
+      "@id" : "ex:id/staff/researcher/researcher1",
+      "@type" : ["odrl:Party", "coral:HospitalResearchMember"],
+      "odrl:partOf" : {"@id" : "ex:groups/researchers"},
+      "rdfs:label" : "Cruz Chance"
+    }
+   ] 
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/ formal-semantics/ontology/evaluation_request.json",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationRequest",
+  "@id": "ex:request/P08-3",
+  "evaluatedAction": "odrl:read",
+  "evaluatedParty": "ex:id/staff/physician/doctor2",
+  "evaluatedTarget": "db:ClinicalRecords?isAnonymized='True'"
+}
+</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "odrl:Set",
+  "uid": "ex:5b5bf495-f6c4-4511-b94f-87410e55d947",
+  "rdfs:label" : "Policy 08",
+  "permission": [
+    {
+      "@type": "odrl:Permission",
+      "assigner": {
+        "@type": [
+          "odrl:Party",
+          "sch:Hospital"
+        ],
+        "uid": "ex:hopital-organization",
+        "rdfs:description" : "A specific hospital that owns this policy"
+      },
+      "assignee": {
+        "@type": [
+          "odrl:PartyCollection",
+          "coral:HospitalResearchMember"
+        ],
+        "uid": "ex:groups/researchers",
+        "rdfs:description": "Any person who is part of the hospital research team"
+      },
+      "action": "read",
+      "target": "db:ClinicalRecords?isAnonymized='True'"
+    }
+  ]
+}
+</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P08-3",
+  "evaluationRequest": "ex:request/P08-3",
+  "policy": "ex:policy/P08",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "doctor2 does not belong to the researchers PartyCollection (coral:HospitalResearchMember). The permission for odrl:read on anonymised clinical records does not apply to this party. Decision: deny."
+}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P08_Research_Anonymized_Data_Only</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ex:5b5bf495-f6c4-4511-b94f-87410e55d947</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -2877,7 +3479,7 @@
 </t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -2889,22 +3491,17 @@
   "@id": "ex:request/P08-1",
   "evaluatedAction": "odrl:read",
   "evaluatedParty": "ex:id/staff/researcher/researcher1",
-  "evaluatedTarget": "db:ClinicalRecords",
-}
-</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:isAnonymized": {
-        "@type": "xsd:boolean"
-      }
-    }
+  "evaluatedTarget": "db:ClinicalRecords?isAnonymized='True'"
+}
+</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "odrl:Set",
   "uid": "ex:5b5bf495-f6c4-4511-b94f-87410e55d947",
@@ -2929,26 +3526,45 @@
         "rdfs:description": "Any person who is part of the hospital research team"
       },
       "action": "read",
-      "target": "db:ClinicalRecords?isAnonymized='True'&amp;records"
+      "target": "db:ClinicalRecords?isAnonymized='True'"
     }
   ]
 }
 </t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P08-1",
+  "evaluationRequest": "ex:request/P08-1",
+  "policy": "ex:policy/P08",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "researcher1 belongs to the researchers PartyCollection (coral:HospitalResearchMember). The target db:ClinicalRecords?isAnonymized='True' satisfies the filtered asset condition. The permission for odrl:read is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>P09_Administrative_Forbidden_to_Create_Appointment_if_Debtor</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>ex:008509f7-41d1-401c-937e-6ae7a1ff369a</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -2980,7 +3596,7 @@
 </t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -3010,7 +3626,7 @@
 </t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -3060,19 +3676,38 @@
 </t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P09-2",
+  "evaluationRequest": "ex:request/P09-2",
+  "policy": "ex:008509f7-41d1-401c-937e-6ae7a1ff369a",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "undefined",
+  "rdfs:comment": "administrator1 belongs to the admin-staff PartyCollection (coral:AdministrativeMember). The param-identity (Y3237068Q) matches a patient_id in db:BillingInformation whose status is NOT DEBTOR. The billing status constraint is not satisfied, so the prohibition is not activated. No permission covers this action either. Decision: undefined (the prohibition does not fire; no explicit permit exists)."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>P09_Administrative_Forbidden_to_Create_Appointment_if_Debtor</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>ex:008509f7-41d1-401c-937e-6ae7a1ff369a</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3104,7 +3739,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -3134,7 +3769,7 @@
 </t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -3184,19 +3819,38 @@
 </t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P09-1",
+  "evaluationRequest": "ex:request/P09-1",
+  "policy": "ex:008509f7-41d1-401c-937e-6ae7a1ff369a",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "forbid",
+  "rdfs:comment": "administrator1 belongs to the admin-staff PartyCollection (coral:AdministrativeMember). The param-identity (33512354C) matches a patient_id in db:BillingInformation whose status is DEBTOR. Both constraints of the prohibition are satisfied. Decision: forbid."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>P10_Nursing_Access_During_Shift_Window</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3221,6 +3875,16 @@
       "@type" : ["odrl:Party", "coral:NurseStaff"],
       "odrl:partOf" : {"@id" : "ex:groups/nursing-staff"},
       "rdfs:label" : "Macy Aina"
+    },{
+      "@id" : "ex:subjectShiftStart",
+      "@type" : "coral:WorkingShiftStarts",
+      "coral:value" : "09:00",
+      "coral:shiftAppliesTo" : "ex:id/staff/nurse/nurse1"
+    },{
+      "@id" : "ex:subjectShiftEnd",
+      "@type" : "coral:WorkingShiftEnds",
+      "coral:value" : "18:00",
+      "coral:shiftAppliesTo" : "ex:id/staff/nurse/nurse1"
     }
    ] 
   }
@@ -3228,7 +3892,7 @@
 </t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -3244,24 +3908,16 @@
 }</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:subjectShiftStart": {
-        "@type": "xsd:time"
-      },
-      "ex:subjectShiftEnd": {
-        "@type": "xsd:time"
-      }
-    }
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "odrl:Set",
   "uid": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
-  "rdfs:label" : "Policy 10",
+  "rdfs:label": "Policy 10",
   "permission": [
     {
       "@type": "odrl:Permission",
@@ -3271,7 +3927,7 @@
           "sch:Hospital"
         ],
         "uid": "ex:hopital-organization",
-        "rdfs:description" : "A specific hospital that owns this policy"
+        "rdfs:description": "A specific hospital that owns this policy"
       },
       "assignee": {
         "@type": [
@@ -3279,7 +3935,7 @@
           "coral:NurseStaff"
         ],
         "uid": "ex:groups/nursing-staff",
-        "rdfs:description" : "Anyone who belongs to the nursing staff"
+        "rdfs:description": "Anyone who belongs to the nursing staff"
       },
       "action": [
         "read",
@@ -3288,41 +3944,56 @@
       "target": "db:MedicationPrescriptions",
       "constraint": [
         {
-          "@type": "odrl:LogicalConstraint",
-          "and": [
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:gteq",
-              "rightOperand": "ex:subjectShiftStart"
-            },
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:lteq",
-              "rightOperand": "ex:subjectShiftEnd"
-            }
-          ]
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:gteq",
+          "rightOperand": "ex:subjectShiftStart"
+        },
+        {
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:lteq",
+          "rightOperand": "ex:subjectShiftEnd"
         }
       ]
     }
   ]
-}</t>
+}
+</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P10-1",
+  "evaluationRequest": "ex:request/P10-1",
+  "policy": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "nurse1 belongs to the nursing-staff PartyCollection (coral:NurseStaff). The state of the world confirms that the current dateTime is within the nurse's shift window (dateTime &gt;= subjectShiftStart AND dateTime &lt;= subjectShiftEnd). The temporal constraint for odrl:read is satisfied and active. Decision: permit."
+}
+</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>P10_Nursing_Access_During_Shift_Window</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3354,7 +4025,7 @@
 </t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -3370,24 +4041,16 @@
 }</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:subjectShiftStart": {
-        "@type": "xsd:time"
-      },
-      "ex:subjectShiftEnd": {
-        "@type": "xsd:time"
-      }
-    }
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "odrl:Set",
   "uid": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
-  "rdfs:label" : "Policy 10",
+  "rdfs:label": "Policy 10",
   "permission": [
     {
       "@type": "odrl:Permission",
@@ -3397,7 +4060,7 @@
           "sch:Hospital"
         ],
         "uid": "ex:hopital-organization",
-        "rdfs:description" : "A specific hospital that owns this policy"
+        "rdfs:description": "A specific hospital that owns this policy"
       },
       "assignee": {
         "@type": [
@@ -3405,7 +4068,7 @@
           "coral:NurseStaff"
         ],
         "uid": "ex:groups/nursing-staff",
-        "rdfs:description" : "Anyone who belongs to the nursing staff"
+        "rdfs:description": "Anyone who belongs to the nursing staff"
       },
       "action": [
         "read",
@@ -3414,41 +4077,56 @@
       "target": "db:MedicationPrescriptions",
       "constraint": [
         {
-          "@type": "odrl:LogicalConstraint",
-          "and": [
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:gteq",
-              "rightOperand": "ex:subjectShiftStart"
-            },
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:lteq",
-              "rightOperand": "ex:subjectShiftEnd"
-            }
-          ]
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:gteq",
+          "rightOperand": "ex:subjectShiftStart"
+        },
+        {
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:lteq",
+          "rightOperand": "ex:subjectShiftEnd"
         }
       ]
     }
   ]
-}</t>
+}
+</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P10-3",
+  "evaluationRequest": "ex:request/P10-3",
+  "policy": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "nurse1 belongs to the nursing-staff PartyCollection (coral:NurseStaff). The state of the world confirms that the current dateTime is within the nurse's shift window. The temporal constraint for odrl:modify is satisfied and active. Decision: permit."
+}
+</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>P10_Nursing_Access_During_Shift_Window</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3480,7 +4158,7 @@
 </t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -3496,24 +4174,16 @@
 }</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:subjectShiftStart": {
-        "@type": "xsd:time"
-      },
-      "ex:subjectShiftEnd": {
-        "@type": "xsd:time"
-      }
-    }
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "odrl:Set",
   "uid": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
-  "rdfs:label" : "Policy 10",
+  "rdfs:label": "Policy 10",
   "permission": [
     {
       "@type": "odrl:Permission",
@@ -3523,7 +4193,7 @@
           "sch:Hospital"
         ],
         "uid": "ex:hopital-organization",
-        "rdfs:description" : "A specific hospital that owns this policy"
+        "rdfs:description": "A specific hospital that owns this policy"
       },
       "assignee": {
         "@type": [
@@ -3531,7 +4201,7 @@
           "coral:NurseStaff"
         ],
         "uid": "ex:groups/nursing-staff",
-        "rdfs:description" : "Anyone who belongs to the nursing staff"
+        "rdfs:description": "Anyone who belongs to the nursing staff"
       },
       "action": [
         "read",
@@ -3540,41 +4210,56 @@
       "target": "db:MedicationPrescriptions",
       "constraint": [
         {
-          "@type": "odrl:LogicalConstraint",
-          "and": [
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:gteq",
-              "rightOperand": "ex:subjectShiftStart"
-            },
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:lteq",
-              "rightOperand": "ex:subjectShiftEnd"
-            }
-          ]
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:gteq",
+          "rightOperand": "ex:subjectShiftStart"
+        },
+        {
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:lteq",
+          "rightOperand": "ex:subjectShiftEnd"
         }
       ]
     }
   ]
-}</t>
+}
+</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P10-2",
+  "evaluationRequest": "ex:request/P10-2",
+  "policy": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "nurse1 belongs to the nursing-staff PartyCollection (coral:NurseStaff). However, the state of the world confirms that the current dateTime is outside the nurse's shift window. The temporal constraint is not satisfied. Decision: deny."
+}
+</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>P10_Nursing_Access_During_Shift_Window</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3606,7 +4291,7 @@
 </t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -3622,24 +4307,16 @@
 }</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:subjectShiftStart": {
-        "@type": "xsd:time"
-      },
-      "ex:subjectShiftEnd": {
-        "@type": "xsd:time"
-      }
-    }
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "odrl:Set",
   "uid": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
-  "rdfs:label" : "Policy 10",
+  "rdfs:label": "Policy 10",
   "permission": [
     {
       "@type": "odrl:Permission",
@@ -3649,7 +4326,7 @@
           "sch:Hospital"
         ],
         "uid": "ex:hopital-organization",
-        "rdfs:description" : "A specific hospital that owns this policy"
+        "rdfs:description": "A specific hospital that owns this policy"
       },
       "assignee": {
         "@type": [
@@ -3657,7 +4334,7 @@
           "coral:NurseStaff"
         ],
         "uid": "ex:groups/nursing-staff",
-        "rdfs:description" : "Anyone who belongs to the nursing staff"
+        "rdfs:description": "Anyone who belongs to the nursing staff"
       },
       "action": [
         "read",
@@ -3666,41 +4343,56 @@
       "target": "db:MedicationPrescriptions",
       "constraint": [
         {
-          "@type": "odrl:LogicalConstraint",
-          "and": [
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:gteq",
-              "rightOperand": "ex:subjectShiftStart"
-            },
-            {
-              "@type": "odrl:Constraint",
-              "leftOperand": "dateTime",
-              "operator": "odrl:lteq",
-              "rightOperand": "ex:subjectShiftEnd"
-            }
-          ]
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:gteq",
+          "rightOperand": "ex:subjectShiftStart"
+        },
+        {
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:lteq",
+          "rightOperand": "ex:subjectShiftEnd"
         }
       ]
     }
   ]
-}</t>
+}
+</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P10-4",
+  "evaluationRequest": "ex:request/P10-4",
+  "policy": "ex:85bc6a9b-1cce-4398-8dd0-859af7390fbb",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "nurse1 belongs to the nursing-staff PartyCollection (coral:NurseStaff). However, the state of the world confirms that the current dateTime is outside the nurse's shift window. The temporal constraint for odrl:modify is not satisfied. Decision: deny."
+}
+</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>P11_Prescription_of_Medications</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>ex:9c8669d7-4403-4cda-8594-6060c9b75c34</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3732,7 +4424,7 @@
 </t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -3749,7 +4441,7 @@
 </t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -3788,19 +4480,38 @@
 }</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P11-1",
+  "evaluationRequest": "ex:request/P11-1",
+  "policy": "ex:policy/P11",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "doctor1 belongs to the medical-staff PartyCollection (sch:Physician). The permission for odrl:use on db:MedicationPrescriptions is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>P11_Prescription_of_Medications</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>ex:9c8669d7-4403-4cda-8594-6060c9b75c34</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3832,7 +4543,7 @@
 </t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -3849,7 +4560,7 @@
 </t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -3888,19 +4599,38 @@
 }</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P11-3",
+  "evaluationRequest": "ex:request/P11-3",
+  "policy": "ex:policy/P11",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "doctor1 belongs to the medical-staff PartyCollection (sch:Physician). The permission for odrl:modify on db:MedicationPrescriptions is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>P11_Prescription_of_Medications</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>ex:9c8669d7-4403-4cda-8594-6060c9b75c34</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -3932,7 +4662,7 @@
 </t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -3949,7 +4679,7 @@
 </t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -3988,19 +4718,38 @@
 }</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P11-2",
+  "evaluationRequest": "ex:request/P11-2",
+  "policy": "ex:policy/P11",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "nurse1 does not belong to the medical-staff PartyCollection (sch:Physician). The permission for odrl:use on db:MedicationPrescriptions does not apply to this party. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>P11_Prescription_of_Medications</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>ex:9c8669d7-4403-4cda-8594-6060c9b75c34</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4032,7 +4781,7 @@
 </t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4049,7 +4798,7 @@
 </t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -4088,19 +4837,38 @@
 }</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P11-4",
+  "evaluationRequest": "ex:request/P11-4",
+  "policy": "ex:policy/P11",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "nurse1 does not belong to the medical-staff PartyCollection (sch:Physician). The permission for odrl:modify on db:MedicationPrescriptions does not apply to this party. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>P12_Pharmaceutical_Dispensing</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>ex:c325c669-d899-408f-967f-2678dc2d377d</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4132,7 +4900,7 @@
 </t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4155,7 +4923,7 @@
 </t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4209,19 +4977,38 @@
 </t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P12-2",
+  "evaluationRequest": "ex:request/P12-2",
+  "policy": "ex:policy/P12",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "pharmacist1 belongs to the pharmacy-staff PartyCollection (coral:Pharmacist). However, the param db:MedicationPrescriptions?status has value DELIVERED, which does not match the PENDING constraint. The permission is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>P12_Pharmaceutical_Dispensing</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>ex:c325c669-d899-408f-967f-2678dc2d377d</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4253,7 +5040,7 @@
 </t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4276,7 +5063,7 @@
 </t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4330,19 +5117,38 @@
 </t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P12-4",
+  "evaluationRequest": "ex:request/P12-4",
+  "policy": "ex:policy/P12",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "pharmacist1 belongs to the pharmacy-staff PartyCollection (coral:Pharmacist). However, the param db:MedicationPrescriptions?status has value DELIVERED, which does not match the PENDING constraint. The permission for odrl:modify is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>P12_Pharmaceutical_Dispensing</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>ex:c325c669-d899-408f-967f-2678dc2d377d</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4374,7 +5180,7 @@
 </t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4397,7 +5203,7 @@
 </t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4451,19 +5257,38 @@
 </t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P12-3",
+  "evaluationRequest": "ex:request/P12-3",
+  "policy": "ex:policy/P12",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "pharmacist1 belongs to the pharmacy-staff PartyCollection (coral:Pharmacist). The param db:MedicationPrescriptions?status has value PENDING, which matches the constraint. The permission for odrl:modify is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>P12_Pharmaceutical_Dispensing</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>ex:c325c669-d899-408f-967f-2678dc2d377d</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4495,7 +5320,7 @@
 </t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4518,7 +5343,7 @@
 </t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4572,19 +5397,38 @@
 </t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P12-1",
+  "evaluationRequest": "ex:request/P12-1",
+  "policy": "ex:policy/P12",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "pharmacist1 belongs to the pharmacy-staff PartyCollection (coral:Pharmacist). The param db:MedicationPrescriptions?status has value PENDING, which matches the constraint. The permission for odrl:read is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>P13_External_Consultation</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>ex:3bd86d6b-7786-4228-8609-a96ef9251f7a</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4611,7 +5455,7 @@
 </t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4634,27 +5478,13 @@
 </t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:referralTargetId": {
-        "@type": "@id"
-      },
-      "ex:subjectId": {
-        "@type": "@id"
-      },
-      "ex:referralExpiry": {
-        "@type": "xsd:dateTime"
-      },
-      "ex:currentTime": {
-        "@type": "xsd:dateTime"
-      }
-    }
-  ],
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+    ],
   "@type": "odrl:Set",
   "uid": "ex:3bd86d6b-7786-4228-8609-a96ef9251f7a",
   "rdfs:label": "Policy 13",
@@ -4697,19 +5527,38 @@
 </t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P13-2",
+  "evaluationRequest": "ex:request/P13-2",
+  "policy": "ex:policy/P13",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "specialist1 belongs to the medical-staff PartyCollection (coral:SpecialistPhysician). However, the current dateTime (2026-08-19T15:00:00) is after the referral expiry date defined in the state of the world. The temporal constraint is not satisfied (referral expired). Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>P13_External_Consultation</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>ex:3bd86d6b-7786-4228-8609-a96ef9251f7a</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4718,7 +5567,7 @@
      "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
     { "@context" : { "member" : { "@id" : "odrl:member", "@type" : "@id" } }}
   ],
-  "@id" : "ex:StateP13-1",
+  "@id" : "ex:StateP13-2",
   "@type" : "SotW",
   "context" :  {
     "@id" : "ex:groups/specialist-staff",
@@ -4736,50 +5585,36 @@
 </t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/ formal-semantics/ontology/evaluation_request.json",
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/formal-semantics/ontology/evaluation_request.json",
     "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
   ],
   "@type": "EvaluationRequest",
-  "@id": "ex:request/P13-1",
+  "@id": "ex:request/P13-3",
   "evaluatedAction": "odrl:read",
-  "evaluatedParty": "ex:id/staff/physician/specialist1",
-  "evaluatedTarget": "db:ClinicalRecords",
+  "evaluatedParty": "ex:id/staff/physician/doctor1",
+  "evaluatedTarget": "db:ClinicalRecords/324145?record_id='AB12'",
   "requestParameters": {
     "@type" : "RequestParameter",
-    "@id" : "ex:request/P13-1/param", 
+    "@id" : "ex:request/P13-3/param",
     "value" : { "@value" : "2026-01-19T15:00:00", "@type" : "xsd:dateTime" },
-    "describesFeature" :  "sotw:CurrentXSDDateTime" 
+    "describesFeature" : "sotw:CurrentXSDDateTime"
   }
 }
 </t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "@context": [
-    "http://www.w3.org/ns/odrl.jsonld",
-    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
-    {
-      "ex:referralTargetId": {
-        "@type": "@id"
-      },
-      "ex:subjectId": {
-        "@type": "@id"
-      },
-      "ex:referralExpiry": {
-        "@type": "xsd:dateTime"
-      },
-      "ex:currentTime": {
-        "@type": "xsd:dateTime"
-      }
-    }
-  ],
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+    ],
   "@type": "odrl:Set",
   "uid": "ex:3bd86d6b-7786-4228-8609-a96ef9251f7a",
   "rdfs:label": "Policy 13",
@@ -4822,19 +5657,168 @@
 </t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P13-3",
+  "evaluationRequest": "ex:request/P13-3",
+  "policy": "ex:3bd86d6b-7786-4228-8609-a96ef9251f7a",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "doctor1 does not belong to the specialist-staff PartyCollection (coral:SpecialistPhysician). The permission applies exclusively to specialist physicians with an active referral. The assignee constraint is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P13_External_Consultation</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ex:3bd86d6b-7786-4228-8609-a96ef9251f7a</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context" : [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/formal-semantics/ontology/stow.json",
+     "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
+    { "@context" : { "member" : { "@id" : "odrl:member", "@type" : "@id" } }}
+  ],
+  "@id" : "ex:StateP13-1",
+  "@type" : "SotW",
+  "context" :  {
+    "@id" : "ex:groups/specialist-staff",
+    "@type" : "odrl:PartyCollection",
+    "rdfs:label" : "Specialist Medical Staff",
+    "member" : [ {
+      "@id" : "ex:id/staff/physician/specialist1",
+      "@type" : ["odrl:Party", "coral:EmergencyPhysician"],
+      "odrl:partOf" : {"@id" : "ex:groups/specialist-staff"},
+      "rdfs:label" : "Dr. Roberto Cheu"
+    }
+   ] 
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/ formal-semantics/ontology/evaluation_request.json",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationRequest",
+  "@id": "ex:request/P13-1",
+  "evaluatedAction": "odrl:read",
+  "evaluatedParty": "ex:id/staff/physician/specialist1",
+  "evaluatedTarget": "db:ClinicalRecords",
+  "requestParameters": {
+    "@type" : "RequestParameter",
+    "@id" : "ex:request/P13-1/param", 
+    "value" : { "@value" : "2026-01-19T15:00:00", "@type" : "xsd:dateTime" },
+    "describesFeature" :  "sotw:CurrentXSDDateTime" 
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+    ],
+  "@type": "odrl:Set",
+  "uid": "ex:3bd86d6b-7786-4228-8609-a96ef9251f7a",
+  "rdfs:label": "Policy 13",
+  "permission": [
+    {
+      "@type": "odrl:Permission",
+      "assigner": {
+        "@type": [
+          "odrl:Party",
+          "sch:Hospital"
+        ],
+        "uid": "ex:hopital-organization",
+        "rdfs:description": "A specific hospital that owns this policy"
+      },
+      "assignee": {
+        "@type": [
+          "odrl:PartyCollection",
+          "coral:SpecialistPhysician"
+        ],
+        "uid": "ex:groups/medical-staff",
+        "vcard:fn": "Anyone who is a specialist physician"
+      },
+      "action": "read",
+      "target": "db:ClinicalRecords/324145?record_id='AB12'",
+      "rdfs:label": "The target specifies the patient (324145) and the specific clinical record (AB12) that can be accessed by the specialist",
+      "constraint": [
+        {
+          "@type": "odrl:Constraint",
+          "leftOperand": "dateTime",
+          "operator": "odrl:lt",
+          "rightOperand": {
+            "@value": "2026-05-04T13:51:59",
+            "@type": "xsd:datetime"
+          }
+        }
+      ]
+    }
+  ]
+}
+</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P13-1",
+  "evaluationRequest": "ex:request/P13-1",
+  "policy": "ex:policy/P13",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "specialist1 belongs to the medical-staff PartyCollection (coral:SpecialistPhysician). The current dateTime (2026-01-19T15:00:00) is before the referral expiry date defined in the state of the world. Both constraints (referral target identity match and temporal validity) are satisfied. Decision: permit."
+}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>P14_Legal_Guardian_Parent_Access_to_Minors</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>ex:b98654ad-1a2a-4f74-9820-f4b260614b71</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4861,7 +5845,7 @@
 </t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4892,7 +5876,7 @@
 </t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -4953,19 +5937,38 @@
 </t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P14-2",
+  "evaluationRequest": "ex:request/P14-2",
+  "policy": "ex:policy/P14",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "familiar1 belongs to the family PartyCollection (coral:LegalGuardian). However, the state of the world confirms that the patient identified by V28514271 is NOT a minor (age &gt;= 18). The age constraint is not satisfied; the policy no longer applies once the patient reaches adulthood. Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>P14_Legal_Guardian_Parent_Access_to_Minors</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>ex:b98654ad-1a2a-4f74-9820-f4b260614b71</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -4992,7 +5995,7 @@
 </t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -5023,7 +6026,7 @@
 </t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -5084,19 +6087,188 @@
 </t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P14-1",
+  "evaluationRequest": "ex:request/P14-1",
+  "policy": "ex:policy/P14",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "familiar1 belongs to the family PartyCollection (coral:LegalGuardian). The state of the world confirms that the patient identified by V28514271 is a minor (age &lt; 18) AND that familiar1 is their registered legal guardian. Both constraints are satisfied. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P14_Legal_Guardian_Parent_Access_to_Minors</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ex:b98654ad-1a2a-4f74-9820-f4b260614b71</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context" : [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/formal-semantics/ontology/stow.json",
+     "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json",
+    { "@context" : { "member" : { "@id" : "odrl:member", "@type" : "@id" } }}
+  ],
+  "@id" : "ex:StateP14-1",
+  "@type" : "SotW",
+  "context" :  {
+    "@id" : "ex:groups/family",
+    "@type" : "odrl:PartyCollection",
+    "rdfs:label" : "Family of underage patient",
+    "member" : [ {
+      "@id" : "ex:id/family/familiar1",
+      "@type" : ["odrl:Party", "sch:Person"],
+      "odrl:partOf" : {"@id" : "ex:groups/family"},
+      "rdfs:label" : "Jason Faught"
+    }
+   ] 
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/w3c/odrl/refs/heads/master/formal-semantics/ontology/evaluation_request.json",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationRequest",
+  "@id": "ex:request/P14-3",
+  "evaluatedAction": "odrl:read",
+  "evaluatedParty": "ex:id/family/familiar2",
+  "evaluatedTarget": "db:ClinicalRecords",
+  "requestParameters": [
+    {
+      "@type" : "RequestParameter",
+      "@id" : "ex:request/P14/param-legal-guardian",
+      "value": "ex:id/family/familiar2",
+      "rdfs:label" : "Legal guardian identity — NOT the registered guardian of this patient"
+    },
+    {
+      "@type" : "RequestParameter",
+      "@id" : "ex:request/P14/param-underage_patient",
+      "value": "V28514271",
+      "rdfs:label" : "The underage patient identity card"
+    }
+  ]
+}
+</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "odrl:Set",
+  "uid": "ex:b98654ad-1a2a-4f74-9820-f4b260614b71",
+  "rdfs:label" : "Policy 14",
+  "permission": [
+    {
+      "@type": "odrl:Permission",
+      "assigner": {
+        "@type": [
+          "odrl:Party",
+          "sch:Hospital"
+        ],
+        "uid": "ex:hopital-organization",
+        "rdfs:description" : "A specific hospital that owns this policy"
+      },
+      "assignee": {
+        "@type": [
+          "odrl:PartyCollection",
+          "coral:LegalGuardian"
+        ],
+        "uid": "ex:groups/family",
+        "rdfs:description" : "One of the legal guardians of an underage patient"
+      },
+      "action": "read",
+      "target": "db:ClinicalRecords",
+      "constraint": [
+        {
+          "@type": "odrl:LogicalConstraint",
+          "and": [
+            {
+              "@type": "odrl:Constraint",
+              "leftOperand": "db:ClinicalRecords?age",
+              "operator": "odrl:lt",
+              "rightOperand": 18
+            },
+            {
+              "@type": "odrl:Constraint",
+              "leftOperand": "ex:request/P14/param-legal-guardian",
+              "operator": "odrl:isPartOf",
+              "rightOperand": "db:ClinicalRecords?legal_guardian"
+            },{
+              "@type": "odrl:Constraint",
+              "leftOperand": "ex:request/P14/param-underage_patient",
+              "operator": "odrl:eq",
+              "rightOperand": "db:ClinicalRecords?patient_id"
+            }
+          ]
+        }
+      ]
+    }
+  ]
+}
+</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P14-3",
+  "evaluationRequest": "ex:request/P14-3",
+  "policy": "ex:b98654ad-1a2a-4f74-9820-f4b260614b71",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "familiar2 belongs to the family PartyCollection (coral:LegalGuardian). However, the param-legal-guardian value (ex:id/family/familiar2) does not match the registered legal_guardian for patient V28514271 in db:ClinicalRecords. The guardian-identity constraint is not satisfied. Decision: deny."
+}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>P15_Laboratory_Entry_of_Results</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>ex:531d8717-6655-4be0-8ce5-a689d33e2f84</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -5128,7 +6300,7 @@
 </t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -5145,7 +6317,7 @@
 </t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -5181,19 +6353,38 @@
 }</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P15-2",
+  "evaluationRequest": "ex:request/P15-2",
+  "policy": "ex:policy/P15",
+  "policySatisfaction": "not-satisfied",
+  "policyActivation": "inactive",
+  "controlDecision": "deny",
+  "rdfs:comment": "technician1 belongs to the lab-staff PartyCollection (coral:LaboratoryTechnician). However, the evaluated action is odrl:read on db:ClinicalRecords, which is not covered by any permission in this policy (P15 only grants odrl:modify on db:LaboratoryTestResults). Decision: deny."
+}
+</t>
+        </is>
+      </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>P15_Laboratory_Entry_of_Results</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>ex:531d8717-6655-4be0-8ce5-a689d33e2f84</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context" : [
@@ -5225,7 +6416,7 @@
 </t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "@context": [
@@ -5242,7 +6433,7 @@
 </t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>{
   "@context": [
@@ -5278,6 +6469,25 @@
 }</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "@context": [
+    "http://www.w3.org/ns/odrl.jsonld",
+    "https://raw.githubusercontent.com/ODRE-Framework/hospital-rls-dataset/refs/heads/main/context.json"
+  ],
+  "@type": "EvaluationReport",
+  "@id": "ex:report/P15-1",
+  "evaluationRequest": "ex:request/P15-1",
+  "policy": "ex:policy/P15",
+  "policySatisfaction": "satisfied",
+  "policyActivation": "active",
+  "controlDecision": "permit",
+  "rdfs:comment": "technician1 belongs to the lab-staff PartyCollection (coral:LaboratoryTechnician). The permission for odrl:modify on db:LaboratoryTestResults is satisfied and active. Decision: permit."
+}
+</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
